--- a/Supplementary_Materials/llm_judge_reliability.xlsx
+++ b/Supplementary_Materials/llm_judge_reliability.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Supplementary_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CD4741-F7C3-4FF2-959A-8427B28B1BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4903A4-7724-4682-BD6A-2DFD1315798A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>deepseek-r1:32b</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,10 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2/50=4%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Average Fluctuation/Manual review rate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -54,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1/50=1%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Average Rate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,6 +79,10 @@
   </si>
   <si>
     <t xml:space="preserve">Agreement but Error Rate-Safe(50 pairs, 100 samples) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/50=2%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -476,19 +472,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -540,19 +536,19 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -563,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>6.7000000000000002E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -577,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>

--- a/Supplementary_Materials/llm_judge_reliability.xlsx
+++ b/Supplementary_Materials/llm_judge_reliability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Supplementary_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4903A4-7724-4682-BD6A-2DFD1315798A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487C3DDC-ED04-4B8A-BDA0-DC4A7AAEAF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
